--- a/A_2018/chrIV:642423-691840_310_finemapping.xlsx
+++ b/A_2018/chrIV:642423-691840_310_finemapping.xlsx
@@ -43876,10 +43876,10 @@
         <v>0.000000707233932333891</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0000544570127897096</v>
+        <v>0.0000551642467220435</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0000521119739614446</v>
+        <v>0.0000528564307323224</v>
       </c>
       <c r="J2" t="s">
         <v>401</v>
@@ -43911,10 +43911,10 @@
         <v>0.000139990315480301</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0053896271459916</v>
+        <v>0.00545962230373175</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00515753793874795</v>
+        <v>0.00523121705215863</v>
       </c>
       <c r="J3" t="s">
         <v>408</v>
